--- a/risk-management/Земляник - Карта рисков.xlsx
+++ b/risk-management/Земляник - Карта рисков.xlsx
@@ -3245,7 +3245,7 @@
       </c>
       <c r="D22" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Низкое — нет AI-объяснений и Cmd-K на время сбоя</t>
+          <t xml:space="preserve">Низкое — нет AI-объяснений и исправлений на время сбоя</t>
         </is>
       </c>
       <c r="E22" s="58" t="inlineStr">

--- a/risk-management/Земляник - Карта рисков.xlsx
+++ b/risk-management/Земляник - Карта рисков.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">Здравствуйте! </t>
   </si>
@@ -128,345 +128,6 @@
   </si>
   <si>
     <t>3 вариант</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>Оценка</t>
-  </si>
-  <si>
-    <t>Описание</t>
-  </si>
-  <si>
-    <t>Пример</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>Очень низкая</t>
-  </si>
-  <si>
-    <t>Единичный случай за 10 лет</t>
-  </si>
-  <si>
-    <t>&lt; 5%</t>
-  </si>
-  <si>
-    <t>Низкая</t>
-  </si>
-  <si>
-    <t>Раз в 2-3 года</t>
-  </si>
-  <si>
-    <t>5-20%</t>
-  </si>
-  <si>
-    <t>Средняя</t>
-  </si>
-  <si>
-    <t>Раз в год</t>
-  </si>
-  <si>
-    <t>20-50%</t>
-  </si>
-  <si>
-    <t>Высокая</t>
-  </si>
-  <si>
-    <t>Несколько раз в год</t>
-  </si>
-  <si>
-    <t>50-80%</t>
-  </si>
-  <si>
-    <t>Очень высокая</t>
-  </si>
-  <si>
-    <t>Регулярно / постоянно</t>
-  </si>
-  <si>
-    <t>&gt; 80%</t>
-  </si>
-  <si>
-    <t>Шкала вероятности </t>
-  </si>
-  <si>
-    <t>Финансовые потери</t>
-  </si>
-  <si>
-    <t>Репутационный ущерб</t>
-  </si>
-  <si>
-    <t>Юридические последствия</t>
-  </si>
-  <si>
-    <t>Очень низкое</t>
-  </si>
-  <si>
-    <t>Локальный</t>
-  </si>
-  <si>
-    <t>Нет</t>
-  </si>
-  <si>
-    <t>Низкое</t>
-  </si>
-  <si>
-    <t>Внутренний</t>
-  </si>
-  <si>
-    <t>Среднее</t>
-  </si>
-  <si>
-    <t>Региональный</t>
-  </si>
-  <si>
-    <t>Высокое</t>
-  </si>
-  <si>
-    <t>Национальный</t>
-  </si>
-  <si>
-    <t>Очень высокое</t>
-  </si>
-  <si>
-    <t>Международный</t>
-  </si>
-  <si>
-    <t>Блокировка деятельности, судебные иски</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Шкала воздействия </t>
-  </si>
-  <si>
-    <t>№</t>
-  </si>
-  <si>
-    <t>Риск</t>
-  </si>
-  <si>
-    <t>Категория</t>
-  </si>
-  <si>
-    <t>Вер</t>
-  </si>
-  <si>
-    <t>Вз</t>
-  </si>
-  <si>
-    <t>Коэфф.</t>
-  </si>
-  <si>
-    <t>Приоритет</t>
-  </si>
-  <si>
-    <t>R1</t>
-  </si>
-  <si>
-    <t>Отсутствие согласий на биометрию</t>
-  </si>
-  <si>
-    <t>Правовой</t>
-  </si>
-  <si>
-    <t>🔴 Высокий</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>Трансграничная передача ПДн</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>Сопротивление сотрудников</t>
-  </si>
-  <si>
-    <t>Организационный</t>
-  </si>
-  <si>
-    <t>🟡 Средний</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>Недостаток компетенций</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>Отказ облачной платформы</t>
-  </si>
-  <si>
-    <t>Технический</t>
-  </si>
-  <si>
-    <t>средний</t>
-  </si>
-  <si>
-    <t>Вероят- ность (1–5)</t>
-  </si>
-  <si>
-    <t>Влияние (1–5)</t>
-  </si>
-  <si>
-    <t>Уровень приоритета (В x Вл)</t>
-  </si>
-  <si>
-    <t>Меры реагирования / Снижение риска</t>
-  </si>
-  <si>
-    <t>Утечка биометрических и иных персональных данных работников</t>
-  </si>
-  <si>
-    <t>20 (Критический)</t>
-  </si>
-  <si>
-    <t>Шифрование данных при хранении и передаче, строгий контроль доступа, DLP-системы, регулярный аудит безопасности, сегментация сети.</t>
-  </si>
-  <si>
-    <t>Несоответствие системы требованиям Закона РБ № 99-З «О защите персональных данных»</t>
-  </si>
-  <si>
-    <t>15 (Высокий)</t>
-  </si>
-  <si>
-    <t>Проведение правового аудита на этапе проектирования, привлечение комплаенс-консультантов, получение разъяснений НЦЗПД.</t>
-  </si>
-  <si>
-    <t>Отсутствие или ненадлежащее оформление согласий субъектов ПД и внутренних ЛПА</t>
-  </si>
-  <si>
-    <t>16 (Высокий)</t>
-  </si>
-  <si>
-    <t>Разработка и утверждение Политики обработки ПД, получение письменных согласий от всех работников, актуализация локальных актов.</t>
-  </si>
-  <si>
-    <t>Нарушение порядка трансграничной передачи ПД и отсутствие соглашения с облачным провайдером</t>
-  </si>
-  <si>
-    <t>Юридическая проверка местонахождения серверов, заключение договора с провайдером с условиями о защите ПД, выбор локализованных облачных решений.</t>
-  </si>
-  <si>
-    <t>Привлечение к административной ответственности по результатам проверки НЦЗПД</t>
-  </si>
-  <si>
-    <t>10 (Средний)</t>
-  </si>
-  <si>
-    <t>Проведение внутренней самопроверки до внедрения, устранение всех замечаний, ведение документированного учета действий с ПД.</t>
-  </si>
-  <si>
-    <t>Несанкционированный доступ к системе «Умный офис» и корпоративной сети через IoT-уязвимости</t>
-  </si>
-  <si>
-    <t>Регулярное обновление прошивок IoT, смена заводских паролей, изоляция IoT-сегмента от корпоративной сети, мониторинг аномалий.</t>
-  </si>
-  <si>
-    <t>Отказ или некорректная работа интеграции между подсистемами</t>
-  </si>
-  <si>
-    <t>12 (Средний)</t>
-  </si>
-  <si>
-    <t>Тщательное тестирование интеграции на стенде, поэтапный ввод в эксплуатацию, наличие резервных каналов связи, SLA с интегратором.</t>
-  </si>
-  <si>
-    <t>Ошибки распознавания лиц (отказ в доступе, ложные срабатывания)</t>
-  </si>
-  <si>
-    <t>Выбор качественного ПО с высоким процентом распознавания, настройка порогов чувствительности, наличие альтернативных методов доступа (карты, пин-коды).</t>
-  </si>
-  <si>
-    <t>Потеря данных вследствие отсутствия или некорректного резервного копирования</t>
-  </si>
-  <si>
-    <t>Настройка автоматического резервного копирования, хранение бэкапов в защищенном сегменте, регулярные проверки восстановления данных.</t>
-  </si>
-  <si>
-    <t>DDoS-атаки и недоступность облачной платформы интегратора</t>
-  </si>
-  <si>
-    <t>Заключение SLA с гарантиями доступности, наличие резервного канала связи, проработка сценариев ручного управления доступом.</t>
-  </si>
-  <si>
-    <t>Нарушение сроков внедрения проекта внешним интегратором</t>
-  </si>
-  <si>
-    <t>Детализированный план-график с вехами, штрафные санкции в договоре, еженедельный мониторинг статуса, выделение внутреннего проектного офиса.</t>
-  </si>
-  <si>
-    <t>Превышение бюджета проекта и доп. расходы на устранение уязвимостей</t>
-  </si>
-  <si>
-    <t>Формирование резервного бюджета (10–15%), фиксация цены в договоре, проведение предварительного аудита безопасности для оценки затрат.</t>
-  </si>
-  <si>
-    <t>Ошибки при настройке прав доступа и избыточные права администраторов</t>
-  </si>
-  <si>
-    <t>Внедрение политики минимальных привилегий, разделение административных ролей, регулярный пересмотр прав доступа, логирование действий админов.</t>
-  </si>
-  <si>
-    <t>Отказ работников использовать биометрию и нецелевое использование видео</t>
-  </si>
-  <si>
-    <t>9 (Средний)</t>
-  </si>
-  <si>
-    <t>Проведение разъяснительной кампании, обучение, получение добровольных согласий, внесение изменений в трудовые договоры / правила внутреннего распорядка.</t>
-  </si>
-  <si>
-    <t>Нарушение лицензионных условий, налоговые и бухгалтерские риски при учете ПО и облачных сервисов</t>
-  </si>
-  <si>
-    <t>8 (Средний)</t>
-  </si>
-  <si>
-    <t>Привлечение налогового консультанта, проверка лицензионной чистоты ПО, корректное отражение в бухучете НМА и облачных расходов.</t>
-  </si>
-  <si>
-    <t>&lt; 500 BYN</t>
-  </si>
-  <si>
-    <t>500-3000 BYN</t>
-  </si>
-  <si>
-    <t>соглашение с провайдером</t>
-  </si>
-  <si>
-    <t>3000-20000 BYN</t>
-  </si>
-  <si>
-    <t>20000-100000 BYN</t>
-  </si>
-  <si>
-    <t>&gt;100 000 BYN</t>
-  </si>
-  <si>
-    <t>Штраф до 25 б.в.</t>
-  </si>
-  <si>
-    <t>Штраф 25-50 б.в.</t>
-  </si>
-  <si>
-    <t>Штраф 50–100 б.в., проверка НЦЗПД</t>
   </si>
 </sst>
 </file>
@@ -1505,10 +1166,10 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'Таблица с рисками'!$F$4:$F$23</c:f>
+              <c:f>'Таблица с рисками'!$F$4:$F$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0.7</c:v>
                 </c:pt>
@@ -1571,10 +1232,10 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Таблица с рисками'!$G$4:$G$23</c:f>
+              <c:f>'Таблица с рисками'!$G$4:$G$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0.8</c:v>
                 </c:pt>
@@ -1639,9 +1300,9 @@
           <c:extLst xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
               <c15:datalabelsRange>
-                <c15:f>'Таблица с рисками'!$B$4:$B$23</c15:f>
+                <c15:f>'Таблица с рисками'!$B$4:$B$22</c15:f>
                 <c15:dlblRangeCache>
-                  <c:ptCount val="20"/>
+                  <c:ptCount val="19"/>
                   <c:pt idx="0">
                     <c:v>R 1 </c:v>
                   </c:pt>
@@ -2123,8 +1784,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Таблица1" displayName="Таблица1" ref="A3:I23">
-  <autoFilter ref="A3:I23" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Таблица1" displayName="Таблица1" ref="A3:I22">
+  <autoFilter ref="A3:I22" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Номер риска" dataDxfId="20"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Обозначение риска" dataDxfId="19"/>
@@ -2137,18 +1798,6 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Мероприятия по минимизации рисков" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5C7D4388-0ECB-415C-9044-26636133F7C3}" name="Таблица2" displayName="Таблица2" ref="B28:E34" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{5C90F1E1-F7D3-4DDC-912C-9EAEBC8C5B86}" name="A" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{CCAA69B9-21F9-4D66-A878-F2690EEF5CA6}" name="B" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{40B17F16-8F26-4C2B-B2A1-BC5CBB28247E}" name="C" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{28B930BA-47C4-4932-B205-F2F4CDD05FC1}" name="D" dataDxfId="3"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -2458,7 +2107,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P68"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.26953125" style="6" customWidth="1"/>
@@ -2582,7 +2231,7 @@
       </c>
       <c r="D5" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Высокое — потеря доверия, отток бета-пользователей, провал критерия приёмки</t>
+          <t xml:space="preserve">Критическое — потеря доверия, отток бета-пользователей, провал критерия приёмки</t>
         </is>
       </c>
       <c r="E5" s="58" t="inlineStr">
@@ -3070,7 +2719,7 @@
       </c>
       <c r="I17" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Снижение. Подача за 6 недель до запуска, прохождение чек-листа валидации, веб-аудит как независимый канал продаж. Ответственный: Фронтенд-разработчик.</t>
+          <t xml:space="preserve">Снижение. Чек-лист валидации AppSource проходится на бете 13.0 и в тестировании 14.0; подача — в первый день работы 15.0 (01.09.2027), проверка до 4 недель укладывается в месяц работы; при задержке публичный запуск идёт через веб-аудит, надстройка публикуется позже. Ответственный: Фронтенд-разработчик.</t>
         </is>
       </c>
     </row>
@@ -3089,7 +2738,7 @@
       </c>
       <c r="D18" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Среднее — распыление ресурсов, срыв сроков MVP</t>
+          <t xml:space="preserve">Низкое — распыление ресурсов, задержка MVP до 2 недель</t>
         </is>
       </c>
       <c r="E18" s="58" t="inlineStr">
@@ -3269,729 +2918,26 @@
         </is>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A23" s="10">
-        <v>20</v>
-      </c>
-      <c r="B23" s="10" t="str">
-        <f>"R "&amp;Таблица1[[#This Row],[Номер риска]]&amp;" "</f>
-        <v xml:space="preserve">R 20 </v>
-      </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10">
-        <f>Таблица1[[#This Row],[Оценка вероятности возникновения риска]]*Таблица1[[#This Row],[Оценка силы воздействия риска]]</f>
-        <v>0</v>
-      </c>
-      <c r="I23" s="10"/>
-    </row>
-    <row r="27" spans="1:16" ht="16" x14ac:dyDescent="0.35">
-      <c r="B27" s="31"/>
-      <c r="C27" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="H27" s="31"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="31"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="33"/>
-      <c r="N27" s="33"/>
-      <c r="O27" s="33"/>
-      <c r="P27" s="33"/>
-    </row>
-    <row r="28" spans="1:16" ht="32" x14ac:dyDescent="0.35">
-      <c r="B28" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" s="31"/>
-      <c r="G28" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="H28" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="I28" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="J28" s="41" t="s">
-        <v>60</v>
-      </c>
-      <c r="K28" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="L28" s="37"/>
-      <c r="M28" s="37"/>
-      <c r="N28" s="37"/>
-      <c r="O28" s="37"/>
-      <c r="P28" s="37"/>
-    </row>
-    <row r="29" spans="1:16" ht="16" x14ac:dyDescent="0.35">
-      <c r="B29" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="D29" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="F29" s="31"/>
-      <c r="G29" s="45">
-        <v>1</v>
-      </c>
-      <c r="H29" s="45" t="s">
-        <v>62</v>
-      </c>
-      <c r="I29" s="45" t="s">
-        <v>139</v>
-      </c>
-      <c r="J29" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="K29" s="45" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="16" x14ac:dyDescent="0.35">
-      <c r="B30" s="42">
-        <v>1</v>
-      </c>
-      <c r="C30" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="E30" s="44" t="s">
-        <v>45</v>
-      </c>
-      <c r="F30" s="31"/>
-      <c r="G30" s="45">
-        <v>2</v>
-      </c>
-      <c r="H30" s="45" t="s">
-        <v>65</v>
-      </c>
-      <c r="I30" s="45" t="s">
-        <v>140</v>
-      </c>
-      <c r="J30" s="45" t="s">
-        <v>66</v>
-      </c>
-      <c r="K30" s="37" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" ht="16" x14ac:dyDescent="0.35">
-      <c r="B31" s="42">
-        <v>2</v>
-      </c>
-      <c r="C31" s="43" t="s">
-        <v>46</v>
-      </c>
-      <c r="D31" s="43" t="s">
-        <v>47</v>
-      </c>
-      <c r="E31" s="44" t="s">
-        <v>48</v>
-      </c>
-      <c r="F31" s="31"/>
-      <c r="G31" s="45">
-        <v>3</v>
-      </c>
-      <c r="H31" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="I31" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="J31" s="45" t="s">
-        <v>68</v>
-      </c>
-      <c r="K31" s="37" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="32" x14ac:dyDescent="0.35">
-      <c r="B32" s="42">
-        <v>3</v>
-      </c>
-      <c r="C32" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="D32" s="43" t="s">
-        <v>50</v>
-      </c>
-      <c r="E32" s="44" t="s">
-        <v>51</v>
-      </c>
-      <c r="F32" s="31"/>
-      <c r="G32" s="45">
-        <v>4</v>
-      </c>
-      <c r="H32" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="J32" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="K32" s="37" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" ht="48" x14ac:dyDescent="0.35">
-      <c r="B33" s="42">
-        <v>4</v>
-      </c>
-      <c r="C33" s="43" t="s">
-        <v>52</v>
-      </c>
-      <c r="D33" s="43" t="s">
-        <v>53</v>
-      </c>
-      <c r="E33" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="F33" s="31"/>
-      <c r="G33" s="45">
-        <v>5</v>
-      </c>
-      <c r="H33" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="I33" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="J33" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="K33" s="45" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" ht="16" x14ac:dyDescent="0.35">
-      <c r="B34" s="46">
-        <v>5</v>
-      </c>
-      <c r="C34" s="47" t="s">
-        <v>55</v>
-      </c>
-      <c r="D34" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="E34" s="48" t="s">
-        <v>57</v>
-      </c>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="31"/>
-      <c r="I34" s="31"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="41"/>
-    </row>
-    <row r="41" spans="2:11" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="C41" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="D41" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E41" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="F41" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="G41" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="H41" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="I41" s="28" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11" ht="33" x14ac:dyDescent="0.35">
-      <c r="C42" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="D42" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="E42" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="F42" s="30">
-        <v>0.8</v>
-      </c>
-      <c r="G42" s="30">
-        <v>0.9</v>
-      </c>
-      <c r="H42" s="29">
-        <v>0.72</v>
-      </c>
-      <c r="I42" s="30" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11" ht="33" x14ac:dyDescent="0.35">
-      <c r="C43" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="D43" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="E43" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="F43" s="30">
-        <v>0.7</v>
-      </c>
-      <c r="G43" s="30">
-        <v>0.8</v>
-      </c>
-      <c r="H43" s="29">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="I43" s="30" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11" ht="33" x14ac:dyDescent="0.35">
-      <c r="C44" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="D44" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="E44" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="F44" s="30">
-        <v>0.6</v>
-      </c>
-      <c r="G44" s="30">
-        <v>0.6</v>
-      </c>
-      <c r="H44" s="29">
-        <v>0.36</v>
-      </c>
-      <c r="I44" s="30" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="C45" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="D45" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="E45" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="F45" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="G45" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="H45" s="29">
-        <v>0.25</v>
-      </c>
-      <c r="I45" s="30" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11" ht="33" x14ac:dyDescent="0.35">
-      <c r="C46" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="D46" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="E46" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="F46" s="30">
-        <v>0.4</v>
-      </c>
-      <c r="G46" s="30">
-        <v>0.8</v>
-      </c>
-      <c r="H46" s="29">
-        <v>0.32</v>
-      </c>
-      <c r="I46" s="30" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="53" spans="3:8" ht="52.5" x14ac:dyDescent="0.35">
-      <c r="C53" s="50" t="s">
-        <v>75</v>
-      </c>
-      <c r="D53" s="50" t="s">
-        <v>76</v>
-      </c>
-      <c r="E53" s="50" t="s">
-        <v>98</v>
-      </c>
-      <c r="F53" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="G53" s="50" t="s">
-        <v>100</v>
-      </c>
-      <c r="H53" s="50" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="54" spans="3:8" ht="70" x14ac:dyDescent="0.35">
-      <c r="C54" s="51">
-        <v>1</v>
-      </c>
-      <c r="D54" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="E54" s="51">
-        <v>4</v>
-      </c>
-      <c r="F54" s="51">
-        <v>5</v>
-      </c>
-      <c r="G54" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="H54" s="51" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="55" spans="3:8" ht="87.5" x14ac:dyDescent="0.35">
-      <c r="C55" s="51">
-        <v>2</v>
-      </c>
-      <c r="D55" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="E55" s="51">
-        <v>3</v>
-      </c>
-      <c r="F55" s="51">
-        <v>5</v>
-      </c>
-      <c r="G55" s="52" t="s">
-        <v>106</v>
-      </c>
-      <c r="H55" s="51" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="56" spans="3:8" ht="87.5" x14ac:dyDescent="0.35">
-      <c r="C56" s="51">
-        <v>3</v>
-      </c>
-      <c r="D56" s="51" t="s">
-        <v>108</v>
-      </c>
-      <c r="E56" s="51">
-        <v>4</v>
-      </c>
-      <c r="F56" s="51">
-        <v>4</v>
-      </c>
-      <c r="G56" s="52" t="s">
-        <v>109</v>
-      </c>
-      <c r="H56" s="51" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="57" spans="3:8" ht="122.5" x14ac:dyDescent="0.35">
-      <c r="C57" s="51">
-        <v>4</v>
-      </c>
-      <c r="D57" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="E57" s="51">
-        <v>3</v>
-      </c>
-      <c r="F57" s="51">
-        <v>5</v>
-      </c>
-      <c r="G57" s="52" t="s">
-        <v>106</v>
-      </c>
-      <c r="H57" s="51" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="58" spans="3:8" ht="87.5" x14ac:dyDescent="0.35">
-      <c r="C58" s="51">
-        <v>5</v>
-      </c>
-      <c r="D58" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="E58" s="51">
-        <v>2</v>
-      </c>
-      <c r="F58" s="51">
-        <v>5</v>
-      </c>
-      <c r="G58" s="52" t="s">
-        <v>114</v>
-      </c>
-      <c r="H58" s="51" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="59" spans="3:8" ht="87.5" x14ac:dyDescent="0.35">
-      <c r="C59" s="51">
-        <v>6</v>
-      </c>
-      <c r="D59" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="E59" s="51">
-        <v>4</v>
-      </c>
-      <c r="F59" s="51">
-        <v>5</v>
-      </c>
-      <c r="G59" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="H59" s="51" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="60" spans="3:8" ht="70" x14ac:dyDescent="0.35">
-      <c r="C60" s="51">
-        <v>7</v>
-      </c>
-      <c r="D60" s="51" t="s">
-        <v>118</v>
-      </c>
-      <c r="E60" s="51">
-        <v>3</v>
-      </c>
-      <c r="F60" s="51">
-        <v>4</v>
-      </c>
-      <c r="G60" s="52" t="s">
-        <v>119</v>
-      </c>
-      <c r="H60" s="51" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="61" spans="3:8" ht="87.5" x14ac:dyDescent="0.35">
-      <c r="C61" s="51">
-        <v>8</v>
-      </c>
-      <c r="D61" s="51" t="s">
-        <v>121</v>
-      </c>
-      <c r="E61" s="51">
-        <v>4</v>
-      </c>
-      <c r="F61" s="51">
-        <v>3</v>
-      </c>
-      <c r="G61" s="52" t="s">
-        <v>119</v>
-      </c>
-      <c r="H61" s="51" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="62" spans="3:8" ht="87.5" x14ac:dyDescent="0.35">
-      <c r="C62" s="51">
-        <v>9</v>
-      </c>
-      <c r="D62" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E62" s="51">
-        <v>3</v>
-      </c>
-      <c r="F62" s="51">
-        <v>5</v>
-      </c>
-      <c r="G62" s="52" t="s">
-        <v>106</v>
-      </c>
-      <c r="H62" s="51" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="63" spans="3:8" ht="70" x14ac:dyDescent="0.35">
-      <c r="C63" s="51">
-        <v>10</v>
-      </c>
-      <c r="D63" s="51" t="s">
-        <v>125</v>
-      </c>
-      <c r="E63" s="51">
-        <v>3</v>
-      </c>
-      <c r="F63" s="51">
-        <v>4</v>
-      </c>
-      <c r="G63" s="52" t="s">
-        <v>119</v>
-      </c>
-      <c r="H63" s="51" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="64" spans="3:8" ht="70" x14ac:dyDescent="0.35">
-      <c r="C64" s="51">
-        <v>11</v>
-      </c>
-      <c r="D64" s="51" t="s">
-        <v>127</v>
-      </c>
-      <c r="E64" s="51">
-        <v>4</v>
-      </c>
-      <c r="F64" s="51">
-        <v>3</v>
-      </c>
-      <c r="G64" s="52" t="s">
-        <v>119</v>
-      </c>
-      <c r="H64" s="51" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="65" spans="3:8" ht="87.5" x14ac:dyDescent="0.35">
-      <c r="C65" s="51">
-        <v>12</v>
-      </c>
-      <c r="D65" s="51" t="s">
-        <v>129</v>
-      </c>
-      <c r="E65" s="51">
-        <v>4</v>
-      </c>
-      <c r="F65" s="51">
-        <v>4</v>
-      </c>
-      <c r="G65" s="52" t="s">
-        <v>109</v>
-      </c>
-      <c r="H65" s="51" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="66" spans="3:8" ht="87.5" x14ac:dyDescent="0.35">
-      <c r="C66" s="51">
-        <v>13</v>
-      </c>
-      <c r="D66" s="51" t="s">
-        <v>131</v>
-      </c>
-      <c r="E66" s="51">
-        <v>4</v>
-      </c>
-      <c r="F66" s="51">
-        <v>4</v>
-      </c>
-      <c r="G66" s="52" t="s">
-        <v>109</v>
-      </c>
-      <c r="H66" s="51" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="67" spans="3:8" ht="87.5" x14ac:dyDescent="0.35">
-      <c r="C67" s="51">
-        <v>14</v>
-      </c>
-      <c r="D67" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="E67" s="51">
-        <v>3</v>
-      </c>
-      <c r="F67" s="51">
-        <v>3</v>
-      </c>
-      <c r="G67" s="52" t="s">
-        <v>134</v>
-      </c>
-      <c r="H67" s="51" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="68" spans="3:8" ht="105" x14ac:dyDescent="0.35">
-      <c r="C68" s="51">
-        <v>15</v>
-      </c>
-      <c r="D68" s="51" t="s">
-        <v>136</v>
-      </c>
-      <c r="E68" s="51">
-        <v>2</v>
-      </c>
-      <c r="F68" s="51">
-        <v>4</v>
-      </c>
-      <c r="G68" s="52" t="s">
-        <v>137</v>
-      </c>
-      <c r="H68" s="51" t="s">
-        <v>138</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A19:I23 D4:E8 H4:I8 A4:B18 D9:I18">
+  <conditionalFormatting sqref="A19:I22 D4:E8 H4:I8 A4:B18 D9:I18">
     <cfRule type="expression" dxfId="23" priority="6">
       <formula>$H4&gt;0.505</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A19:I23 D4:E8 H4:I8 A4:B18 D9:I18">
+  <conditionalFormatting sqref="A19:I22 D4:E8 H4:I8 A4:B18 D9:I18">
     <cfRule type="expression" dxfId="22" priority="5">
       <formula>AND($H4&lt;0.14,$H4&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A19:I23 D4:E8 H4:I8 A4:B18 D9:I18">
+  <conditionalFormatting sqref="A19:I22 D4:E8 H4:I8 A4:B18 D9:I18">
     <cfRule type="expression" dxfId="21" priority="1">
       <formula>AND($H4&lt;=0.505,$H4&gt;=0.14)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <tableParts count="2">
+  <tableParts count="1">
     <tablePart r:id="rId1"/>
-    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4051,21 +2997,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="Y14" s="6">
-        <v>3232</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="X22" s="6">
-        <v>1212</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="U23" s="6">
-        <v>121</v>
-      </c>
-    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35"/>
     <row r="25" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
         <v>20</v>

--- a/risk-management/Земляник - Карта рисков.xlsx
+++ b/risk-management/Земляник - Карта рисков.xlsx
@@ -2329,7 +2329,7 @@
       </c>
       <c r="I7" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Снижение. Ворота фаз, еженедельный контроль по диаграмме Ганта, MoSCoW — перенос Should в v2, AI-агенты для типового кода. Ответственный: Руководитель проекта.</t>
+          <t xml:space="preserve">Снижение. Ворота фаз, еженедельный контроль по диаграмме Ганта; при отставании более 2 недель — второй бэкенд-разработчик и подрядчик на критические работы за счёт резерва; AI-агенты для типового кода; Should и Could в план не входят, объём Must не расширяется. Ответственный: Руководитель проекта.</t>
         </is>
       </c>
     </row>

--- a/risk-management/Земляник - Карта рисков.xlsx
+++ b/risk-management/Земляник - Карта рисков.xlsx
@@ -2961,7 +2961,7 @@
     <row r="1" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="str">
         <f>"Карта рисков для проекта "&amp;'Таблица с рисками'!C1</f>
-        <v xml:space="preserve">Карта рисков для проекта </v>
+        <v xml:space="preserve">Карта рисков для проекта TableMind — AI-сервис проверки Excel-моделей (веб-аудит + надстройка Excel)</v>
       </c>
     </row>
     <row r="2" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">

--- a/risk-management/Земляник - Карта рисков.xlsx
+++ b/risk-management/Земляник - Карта рисков.xlsx
@@ -1,29 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inna\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\excel-mcp-files\project-management-tablemind\risk-management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6D03FC2-842F-4B00-ACE7-FDBB7D49757A}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F670DC-2B51-460D-B099-AF9B79F3305B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="9BSvA8ngIgRbPGpWQYu5c6jXc2vUrBmIIbqdW5FKPKGkzFmbCuUi/d+R6oxi8fpq/L9oObBRRCOKuw2SEVGVJA==" workbookSaltValue="6v36ypmqVNgk/okiC8jG3Q==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6940" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3008" yWindow="458" windowWidth="12022" windowHeight="10972" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Приветствие" sheetId="1" r:id="rId1"/>
     <sheet name="Таблица с рисками" sheetId="2" r:id="rId2"/>
     <sheet name="Карта рисков" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="179021" refMode="R1C1" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="112">
   <si>
     <t xml:space="preserve">Здравствуйте! </t>
   </si>
@@ -128,13 +142,244 @@
   </si>
   <si>
     <t>3 вариант</t>
+  </si>
+  <si>
+    <t>TableMind — AI-сервис проверки Excel-моделей (веб-аудит + надстройка Excel)</t>
+  </si>
+  <si>
+    <t>Крупные платформы (Microsoft Copilot, ChatGPT / Claude for Excel) выпустят бесплатный «режим проверки»</t>
+  </si>
+  <si>
+    <t>Высокое — потеря уникальности, падение конверсии и выручки</t>
+  </si>
+  <si>
+    <t>Анонс функции аудита или верификации у лидеров рынка</t>
+  </si>
+  <si>
+    <t>Снижение. Фокус на нише аудита финмоделей; сверка текста с таблицей и provenance; API/MCP как слой проверки для чужих AI-агентов; ежемесячный мониторинг конкурентов. Ответственный: Владелец продукта.</t>
+  </si>
+  <si>
+    <t>Высокая доля ложных срабатываний правил (precision критичных находок &lt; 90%)</t>
+  </si>
+  <si>
+    <t>Критическое — потеря доверия, отток бета-пользователей, провал критерия приёмки</t>
+  </si>
+  <si>
+    <t>Доля подавленных находок &gt; 15%; precision ниже порога в CI</t>
+  </si>
+  <si>
+    <t>Снижение. Precision — главная метрика; чистый eval-набор; уровни серьёзности; подавление правил; правило выпускается только после прохождения eval. Ответственный: ML/LLM-инженер.</t>
+  </si>
+  <si>
+    <t>Пользователи не захотят менять привычную работу в Excel и пробовать новый сервис</t>
+  </si>
+  <si>
+    <t>Критическое — нет активации и продаж — продукт не подтверждает ценность</t>
+  </si>
+  <si>
+    <t>Менее 8% посетителей начинают аудит; нет повторных аудитов</t>
+  </si>
+  <si>
+    <t>Снижение. Старт с веб-аудита без установки и надстройки внутри Excel; собственный редактор — только после подтверждения спроса; бесплатный тизер находок. Ответственный: Владелец продукта.</t>
+  </si>
+  <si>
+    <t>Срыв сроков критического пути из-за недооценки трудоёмкости (ядро, надстройка)</t>
+  </si>
+  <si>
+    <t>Высокое — сдвиг релиза, рост затрат на оплату труда</t>
+  </si>
+  <si>
+    <t>Отставание &gt; 2 недель от базового плана на воротах</t>
+  </si>
+  <si>
+    <t>Пользователи не готовы загружать конфиденциальные финмодели в облако</t>
+  </si>
+  <si>
+    <t>Высокое — низкая активация, мало данных для проверки ценности</t>
+  </si>
+  <si>
+    <t>Отказы на шаге загрузки &gt; 70%</t>
+  </si>
+  <si>
+    <t>Снижение. Блок доверия у загрузчика, хостинг в ЕС, удаление файлов по сроку, отказ от обучения на данных, демо-файл «проверить на примере». Ответственный: Руководитель проекта.</t>
+  </si>
+  <si>
+    <t>Сложные элементы xlsx (объединённые ячейки, массивы, локали, внешние ссылки) — расхождение пересчёта с Excel</t>
+  </si>
+  <si>
+    <t>Среднее — ошибочные находки, сдвиг сроков разработки ядра</t>
+  </si>
+  <si>
+    <t>Доля ошибок парсинга &gt; 5% на eval-наборе</t>
+  </si>
+  <si>
+    <t>Снижение. Набор эталонных книг; сложные элементы только читаются с предупреждением и пометкой «проверено частично». Ответственный: Бэкенд-разработчик 2.</t>
+  </si>
+  <si>
+    <t>Уход или выгорание ключевого разработчика ядра верификации</t>
+  </si>
+  <si>
+    <t>Высокое — потеря знаний, срыв сроков критического пути</t>
+  </si>
+  <si>
+    <t>Снижение вовлечённости, переработки, внешнее предложение о работе</t>
+  </si>
+  <si>
+    <t>Снижение. ADR и документация, обязательное код-ревью, совместное владение ядром двумя разработчиками, контроль нагрузки. Ответственный: Руководитель проекта.</t>
+  </si>
+  <si>
+    <t>Рост цен или изменение условий LLM API</t>
+  </si>
+  <si>
+    <t>Среднее — снижение валовой маржи ниже 65%</t>
+  </si>
+  <si>
+    <t>Стоимость LLM &gt; 30% выручки на пользователя</t>
+  </si>
+  <si>
+    <t>Снижение. LLM gateway с несколькими провайдерами, кэш промптов, эвристики до вызова LLM, лимиты тарифов. Ответственный: ML/LLM-инженер.</t>
+  </si>
+  <si>
+    <t>Низкая конверсия Free → платный тариф (&lt; 2%)</t>
+  </si>
+  <si>
+    <t>Высокое — цель «≥ 50 платящих пользователей» не достигнута</t>
+  </si>
+  <si>
+    <t>Конверсия &lt; 2% через месяц после запуска оплаты</t>
+  </si>
+  <si>
+    <t>Снижение. Оплата в точке максимальной ценности («исправить и скачать»), разовый аудит 9 €, пробный Pro 7 дней, A/B-тест цен. Ответственный: Владелец продукта.</t>
+  </si>
+  <si>
+    <t>Превышение бюджета проекта</t>
+  </si>
+  <si>
+    <t>Среднее — нехватка средств на запуск и маркетинг</t>
+  </si>
+  <si>
+    <t>Освоение бюджета опережает план более чем на 10%</t>
+  </si>
+  <si>
+    <t>Принятие. Резерв 10% от базовой стоимости (47 000 BYN), ежемесячный контроль затрат, приоритизация Must have. Ответственный: Руководитель проекта.</t>
+  </si>
+  <si>
+    <t>Лицензия движка пересчёта формул (например, GPLv3) несовместима с закрытым SaaS</t>
+  </si>
+  <si>
+    <t>Высокое — замена библиотеки, +1–2 месяца на критическом пути</t>
+  </si>
+  <si>
+    <t>Выбрана библиотека с copyleft-лицензией</t>
+  </si>
+  <si>
+    <t>Уклонение. Проверка лицензий на этапе архитектуры, выбор permissive-библиотек или собственный пересчёт, проверка лицензий в CI. Ответственный: Бэкенд-разработчик 1.</t>
+  </si>
+  <si>
+    <t>Не удастся привлечь 10–20 пилотных пользователей с реальными финмоделями</t>
+  </si>
+  <si>
+    <t>Высокое — нерепрезентативный eval-набор, правила настроены «вслепую»</t>
+  </si>
+  <si>
+    <t>К концу 2-го месяца &lt; 5 пилотных пользователей</t>
+  </si>
+  <si>
+    <t>Снижение. Прямой выход на бухгалтерские и консалтинговые фирмы, бесплатный аудит шаблона, открытые финмодели как резерв. Ответственный: Руководитель проекта.</t>
+  </si>
+  <si>
+    <t>Нарушение GDPR / Закона РБ № 99-З «О защите персональных данных» при передаче данных LLM-провайдеру</t>
+  </si>
+  <si>
+    <t>Критическое — штрафы, блокировка обработки, репутационный ущерб</t>
+  </si>
+  <si>
+    <t>Нет DPA с провайдером; провайдер без обработки в ЕС</t>
+  </si>
+  <si>
+    <t>Уклонение. Только провайдеры с zero data retention и регионом ЕС; DPA; реестр обработки; в LLM передаётся профиль таблицы, а не весь файл. Ответственный: Руководитель проекта (юрист).</t>
+  </si>
+  <si>
+    <t>Задержка или отказ в публикации надстройки в Microsoft AppSource</t>
+  </si>
+  <si>
+    <t>Среднее — сдвиг публичного релиза основного продукта</t>
+  </si>
+  <si>
+    <t>Замечания валидации AppSource; проверка дольше 4 недель</t>
+  </si>
+  <si>
+    <t>Снижение. Чек-лист валидации AppSource проходится на бете 13.0 и в тестировании 14.0; подача — в первый день работы 15.0 (01.09.2027), проверка до 4 недель укладывается в месяц работы; при задержке публичный запуск идёт через веб-аудит, надстройка публикуется позже. Ответственный: Фронтенд-разработчик.</t>
+  </si>
+  <si>
+    <t>Раздувание требований (собственный редактор, коннекторы, Google Sheets)</t>
+  </si>
+  <si>
+    <t>Низкое — распыление ресурсов, задержка MVP до 2 недель</t>
+  </si>
+  <si>
+    <t>Запросы вне списка Must/Should от заказчика и бета-пользователей</t>
+  </si>
+  <si>
+    <t>Уклонение. Зафиксированный список Won’t have, процедура управления изменениями, бэклог v2. Ответственный: Владелец продукта.</t>
+  </si>
+  <si>
+    <t>Утечка файлов клиентов (ошибка разграничения доступа, взлом)</t>
+  </si>
+  <si>
+    <t>Критическое — штрафы, потеря доверия, закрытие B2B-продаж</t>
+  </si>
+  <si>
+    <t>Аномальные запросы к хранилищу; критическая уязвимость в зависимостях</t>
+  </si>
+  <si>
+    <t>Снижение + передача. RLS по воркспейсу, шифрование, песочница без сети, сканирование зависимостей, пентест; страхование киберрисков. Ответственный: Бэкенд-разработчик 1.</t>
+  </si>
+  <si>
+    <t>Prompt injection через содержимое ячеек и текста документа</t>
+  </si>
+  <si>
+    <t>Среднее — искажённые планы агента, утечка системного промпта</t>
+  </si>
+  <si>
+    <t>Внедрённые инструкции из тестового набора проходят фильтр</t>
+  </si>
+  <si>
+    <t>Снижение. Данные в помеченных блоках, у агента нет инструментов с внешними эффектами, верификация каждого плана. Ответственный: ML/LLM-инженер.</t>
+  </si>
+  <si>
+    <t>Искажение структуры, стилей или диаграмм xlsx при экспорте исправленного файла</t>
+  </si>
+  <si>
+    <t>Среднее — пользователь получает повреждённую книгу, потеря доверия к исправлениям</t>
+  </si>
+  <si>
+    <t>Регрессионный тест «до/после экспорта» показывает отличия вне исправленных ячеек</t>
+  </si>
+  <si>
+    <t>Снижение. Точечная правка XML внутри исходного пакета xlsx вместо пересохранения; регрессионный тест экспорта; проверка открытия в Excel для Windows, Mac и веб. Ответственный: Бэкенд-разработчик 1.</t>
+  </si>
+  <si>
+    <t>Временная недоступность провайдера LLM</t>
+  </si>
+  <si>
+    <t>Низкое — нет AI-объяснений и исправлений на время сбоя</t>
+  </si>
+  <si>
+    <t>Ошибки или таймауты API &gt; 5% за час</t>
+  </si>
+  <si>
+    <t>Принятие. Проверки работают без LLM; шаблонные объяснения из каталога правил; переключение провайдера в gateway. Ответственный: ML/LLM-инженер.</t>
+  </si>
+  <si>
+    <t>Снижение. Ворота фаз, еженедельный контроль по диаграмме Ганта; при отставании более 2 недель — подключение бэкенд-разработчика 1 к работам ядра и надстройки и подрядчик за счёт резерва; AI-агенты для типового кода; Should и Could в план не входят, объём Must не расширяется. Ответственный: Руководитель проекта.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,107 +469,6 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri Light"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -376,7 +520,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -425,82 +569,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
@@ -560,76 +634,11 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -643,18 +652,12 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="15">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -678,238 +681,6 @@
           <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1121,6 +892,652 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{A472CF88-F27F-40EB-BA30-730A2A418C8E}" type="CELLRANGE">
+                      <a:rPr lang="ru-RU"/>
+                      <a:pPr/>
+                      <a:t>[ДИАПАЗОН ЯЧЕЕК]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-0D1F-420C-AA59-7E7119F69CA4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{241F6741-F155-41F9-9225-EA8CE1F4CC59}" type="CELLRANGE">
+                      <a:rPr lang="ru-RU"/>
+                      <a:pPr/>
+                      <a:t>[ДИАПАЗОН ЯЧЕЕК]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-0D1F-420C-AA59-7E7119F69CA4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{D53F82D9-7BC4-496B-BDD6-5AB7EF2578BC}" type="CELLRANGE">
+                      <a:rPr lang="ru-RU"/>
+                      <a:pPr/>
+                      <a:t>[ДИАПАЗОН ЯЧЕЕК]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-0D1F-420C-AA59-7E7119F69CA4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{F9C689A5-0F0E-431A-B702-BF62F17879A1}" type="CELLRANGE">
+                      <a:rPr lang="ru-RU"/>
+                      <a:pPr/>
+                      <a:t>[ДИАПАЗОН ЯЧЕЕК]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-0D1F-420C-AA59-7E7119F69CA4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{F8E50C71-2180-4D5C-98CC-857FEFFFE86C}" type="CELLRANGE">
+                      <a:rPr lang="ru-RU"/>
+                      <a:pPr/>
+                      <a:t>[ДИАПАЗОН ЯЧЕЕК]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-0D1F-420C-AA59-7E7119F69CA4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{2EE29D70-69AD-4A36-8144-AFAC46C66B49}" type="CELLRANGE">
+                      <a:rPr lang="ru-RU"/>
+                      <a:pPr/>
+                      <a:t>[ДИАПАЗОН ЯЧЕЕК]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-0D1F-420C-AA59-7E7119F69CA4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{61411894-5808-4A8D-982F-BB48FB7153A5}" type="CELLRANGE">
+                      <a:rPr lang="ru-RU"/>
+                      <a:pPr/>
+                      <a:t>[ДИАПАЗОН ЯЧЕЕК]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-0D1F-420C-AA59-7E7119F69CA4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{CA39AD74-0160-4670-94A6-C96D628EEFFA}" type="CELLRANGE">
+                      <a:rPr lang="ru-RU"/>
+                      <a:pPr/>
+                      <a:t>[ДИАПАЗОН ЯЧЕЕК]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-0D1F-420C-AA59-7E7119F69CA4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{4882C515-F409-436A-A497-A65701EA71D6}" type="CELLRANGE">
+                      <a:rPr lang="ru-RU"/>
+                      <a:pPr/>
+                      <a:t>[ДИАПАЗОН ЯЧЕЕК]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-0D1F-420C-AA59-7E7119F69CA4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{66E1A1FC-8CA2-46D3-B905-64FB9EAE6E74}" type="CELLRANGE">
+                      <a:rPr lang="ru-RU"/>
+                      <a:pPr/>
+                      <a:t>[ДИАПАЗОН ЯЧЕЕК]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-0D1F-420C-AA59-7E7119F69CA4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{71BD2997-E8FE-4B7B-B679-3EA2DD2C806B}" type="CELLRANGE">
+                      <a:rPr lang="ru-RU"/>
+                      <a:pPr/>
+                      <a:t>[ДИАПАЗОН ЯЧЕЕК]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000A-0D1F-420C-AA59-7E7119F69CA4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{2479569C-09F6-454F-A70A-56C1E894EBDC}" type="CELLRANGE">
+                      <a:rPr lang="ru-RU"/>
+                      <a:pPr/>
+                      <a:t>[ДИАПАЗОН ЯЧЕЕК]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000B-0D1F-420C-AA59-7E7119F69CA4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{70A2F2AB-4276-43DA-9195-26EC6F90ADAB}" type="CELLRANGE">
+                      <a:rPr lang="ru-RU"/>
+                      <a:pPr/>
+                      <a:t>[ДИАПАЗОН ЯЧЕЕК]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000C-0D1F-420C-AA59-7E7119F69CA4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="13"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{C0D6E6E2-66CF-45EB-8A32-A5E43AED6D16}" type="CELLRANGE">
+                      <a:rPr lang="ru-RU"/>
+                      <a:pPr/>
+                      <a:t>[ДИАПАЗОН ЯЧЕЕК]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000D-0D1F-420C-AA59-7E7119F69CA4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="14"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{D4FE58AE-8E9C-45E3-BD14-9DFFE8837855}" type="CELLRANGE">
+                      <a:rPr lang="ru-RU"/>
+                      <a:pPr/>
+                      <a:t>[ДИАПАЗОН ЯЧЕЕК]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000E-0D1F-420C-AA59-7E7119F69CA4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="15"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{DE503E4F-1352-4D48-85B3-338D8B163096}" type="CELLRANGE">
+                      <a:rPr lang="ru-RU"/>
+                      <a:pPr/>
+                      <a:t>[ДИАПАЗОН ЯЧЕЕК]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000F-0D1F-420C-AA59-7E7119F69CA4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="16"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{BCF126BB-9884-4971-95E9-E56EBA806F6C}" type="CELLRANGE">
+                      <a:rPr lang="ru-RU"/>
+                      <a:pPr/>
+                      <a:t>[ДИАПАЗОН ЯЧЕЕК]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000010-0D1F-420C-AA59-7E7119F69CA4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="17"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{F6F5CDCF-FC2D-4235-BAB6-64A099080769}" type="CELLRANGE">
+                      <a:rPr lang="ru-RU"/>
+                      <a:pPr/>
+                      <a:t>[ДИАПАЗОН ЯЧЕЕК]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000011-0D1F-420C-AA59-7E7119F69CA4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="18"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{C1F446E9-7E43-4D0C-A079-94D7681E4926}" type="CELLRANGE">
+                      <a:rPr lang="ru-RU"/>
+                      <a:pPr/>
+                      <a:t>[ДИАПАЗОН ЯЧЕЕК]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000012-0D1F-420C-AA59-7E7119F69CA4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -1157,6 +1574,7 @@
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showDataLabelsRange val="1"/>
@@ -1282,7 +1700,7 @@
                   <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>0.6</c:v>
@@ -1297,7 +1715,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+          <c:extLst xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
               <c15:datalabelsRange>
                 <c15:f>'Таблица с рисками'!$B$4:$B$22</c15:f>
@@ -1787,15 +2205,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Таблица1" displayName="Таблица1" ref="A3:I22">
   <autoFilter ref="A3:I22" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Номер риска" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Обозначение риска" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Наименование риска" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Влияние риска на проект/предприятие" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Что является триггером для проявление данного риска?" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Оценка вероятности возникновения риска" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Оценка силы воздействия риска" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Итоговый коэффициент " dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Мероприятия по минимизации рисков" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Номер риска" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Обозначение риска" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Наименование риска" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Влияние риска на проект/предприятие" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Что является триггером для проявление данного риска?" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Оценка вероятности возникновения риска" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Оценка силы воздействия риска" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Итоговый коэффициент " dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Мероприятия по минимизации рисков" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2012,9 +2430,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="F4:Q9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="4" spans="6:17" ht="26" x14ac:dyDescent="0.6">
+    <row r="4" spans="6:17" ht="25.5" x14ac:dyDescent="0.75">
       <c r="F4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2028,7 +2446,7 @@
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="6:17" ht="57.65" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="6:17" ht="57.7" customHeight="1" x14ac:dyDescent="0.75">
       <c r="F5" s="3" t="s">
         <v>1</v>
       </c>
@@ -2044,23 +2462,23 @@
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
     </row>
-    <row r="6" spans="6:17" ht="36" x14ac:dyDescent="0.8">
-      <c r="F6" s="54" t="s">
+    <row r="6" spans="6:17" ht="36" x14ac:dyDescent="1.05">
+      <c r="F6" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="54"/>
-      <c r="M6" s="54"/>
-      <c r="N6" s="54"/>
-      <c r="O6" s="54"/>
-      <c r="P6" s="54"/>
-      <c r="Q6" s="54"/>
-    </row>
-    <row r="7" spans="6:17" ht="26" x14ac:dyDescent="0.6">
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="31"/>
+    </row>
+    <row r="7" spans="6:17" ht="25.5" x14ac:dyDescent="0.75">
       <c r="F7" s="5"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -2074,10 +2492,10 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
     </row>
-    <row r="8" spans="6:17" ht="26" x14ac:dyDescent="0.6">
+    <row r="8" spans="6:17" ht="25.5" x14ac:dyDescent="0.75">
       <c r="F8" s="5"/>
     </row>
-    <row r="9" spans="6:17" ht="26" x14ac:dyDescent="0.6">
+    <row r="9" spans="6:17" ht="25.5" x14ac:dyDescent="0.75">
       <c r="F9" s="5"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
@@ -2108,39 +2526,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" style="6" customWidth="1"/>
-    <col min="2" max="2" width="13.7265625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="60.54296875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="26.26953125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="24.54296875" style="6" customWidth="1"/>
+    <col min="1" max="1" width="7.265625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="13.73046875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="60.53125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="26.265625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="24.53125" style="6" customWidth="1"/>
     <col min="6" max="7" width="19" style="6" customWidth="1"/>
-    <col min="8" max="8" width="47.54296875" style="6" customWidth="1"/>
-    <col min="9" max="9" width="40.1796875" style="6" customWidth="1"/>
-    <col min="10" max="10" width="22.54296875" style="6" customWidth="1"/>
-    <col min="11" max="11" width="19.7265625" style="6" customWidth="1"/>
-    <col min="12" max="12" width="11.1796875" style="6" customWidth="1"/>
-    <col min="13" max="13" width="12.26953125" style="6" customWidth="1"/>
-    <col min="14" max="14" width="16.453125" style="6" customWidth="1"/>
-    <col min="15" max="15" width="26.453125" style="6" customWidth="1"/>
-    <col min="16" max="16" width="25.81640625" style="6" customWidth="1"/>
-    <col min="17" max="16384" width="8.7265625" style="6"/>
+    <col min="8" max="8" width="47.53125" style="6" customWidth="1"/>
+    <col min="9" max="9" width="40.19921875" style="6" customWidth="1"/>
+    <col min="10" max="10" width="22.53125" style="6" customWidth="1"/>
+    <col min="11" max="11" width="19.73046875" style="6" customWidth="1"/>
+    <col min="12" max="12" width="11.19921875" style="6" customWidth="1"/>
+    <col min="13" max="13" width="12.265625" style="6" customWidth="1"/>
+    <col min="14" max="14" width="16.46484375" style="6" customWidth="1"/>
+    <col min="15" max="15" width="26.46484375" style="6" customWidth="1"/>
+    <col min="16" max="16" width="25.796875" style="6" customWidth="1"/>
+    <col min="17" max="16384" width="8.73046875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TableMind — AI-сервис проверки Excel-моделей (веб-аудит + надстройка Excel)</t>
-        </is>
+      <c r="C1" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="F2" s="9" t="s">
         <v>4</v>
       </c>
@@ -2148,7 +2564,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="10" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" s="10" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" s="11" t="s">
         <v>5</v>
       </c>
@@ -2177,7 +2593,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" ht="78" customHeight="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="10">
         <v>1</v>
       </c>
@@ -2185,38 +2601,30 @@
         <f>"R "&amp;Таблица1[[#This Row],[Номер риска]]&amp;" "</f>
         <v xml:space="preserve">R 1 </v>
       </c>
-      <c r="C4" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Крупные платформы (Microsoft Copilot, ChatGPT / Claude for Excel) выпустят бесплатный «режим проверки»</t>
-        </is>
-      </c>
-      <c r="D4" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Высокое — потеря уникальности, падение конверсии и выручки</t>
-        </is>
-      </c>
-      <c r="E4" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Анонс функции аудита или верификации у лидеров рынка</t>
-        </is>
-      </c>
-      <c r="F4" s="30">
+      <c r="C4" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="28">
         <v>0.7</v>
       </c>
-      <c r="G4" s="30">
+      <c r="G4" s="28">
         <v>0.8</v>
       </c>
       <c r="H4" s="10">
         <f>Таблица1[[#This Row],[Оценка вероятности возникновения риска]]*Таблица1[[#This Row],[Оценка силы воздействия риска]]</f>
-        <v>0.56</v>
-      </c>
-      <c r="I4" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Снижение. Фокус на нише аудита финмоделей; сверка текста с таблицей и provenance; API/MCP как слой проверки для чужих AI-агентов; ежемесячный мониторинг конкурентов. Ответственный: Владелец продукта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="78" customHeight="1" spans="1:9" x14ac:dyDescent="0.35">
+        <v>0.55999999999999994</v>
+      </c>
+      <c r="I4" s="30" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="10">
         <v>2</v>
       </c>
@@ -2224,38 +2632,30 @@
         <f>"R "&amp;Таблица1[[#This Row],[Номер риска]]&amp;" "</f>
         <v xml:space="preserve">R 2 </v>
       </c>
-      <c r="C5" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Высокая доля ложных срабатываний правил (precision критичных находок &lt; 90%)</t>
-        </is>
-      </c>
-      <c r="D5" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Критическое — потеря доверия, отток бета-пользователей, провал критерия приёмки</t>
-        </is>
-      </c>
-      <c r="E5" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Доля подавленных находок &gt; 15%; precision ниже порога в CI</t>
-        </is>
-      </c>
-      <c r="F5" s="30">
+      <c r="C5" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="28">
         <v>0.6</v>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="28">
         <v>0.9</v>
       </c>
       <c r="H5" s="10">
         <f>Таблица1[[#This Row],[Оценка вероятности возникновения риска]]*Таблица1[[#This Row],[Оценка силы воздействия риска]]</f>
         <v>0.54</v>
       </c>
-      <c r="I5" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Снижение. Precision — главная метрика; чистый eval-набор; уровни серьёзности; подавление правил; правило выпускается только после прохождения eval. Ответственный: ML/LLM-инженер.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="78" customHeight="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I5" s="30" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="10">
         <v>3</v>
       </c>
@@ -2263,38 +2663,30 @@
         <f>"R "&amp;Таблица1[[#This Row],[Номер риска]]&amp;" "</f>
         <v xml:space="preserve">R 3 </v>
       </c>
-      <c r="C6" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Пользователи не захотят менять привычную работу в Excel и пробовать новый сервис</t>
-        </is>
-      </c>
-      <c r="D6" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Критическое — нет активации и продаж — продукт не подтверждает ценность</t>
-        </is>
-      </c>
-      <c r="E6" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Менее 8% посетителей начинают аудит; нет повторных аудитов</t>
-        </is>
-      </c>
-      <c r="F6" s="53">
+      <c r="C6" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="29">
         <v>0.7</v>
       </c>
-      <c r="G6" s="53">
+      <c r="G6" s="29">
         <v>0.9</v>
       </c>
       <c r="H6" s="10">
         <f>Таблица1[[#This Row],[Оценка вероятности возникновения риска]]*Таблица1[[#This Row],[Оценка силы воздействия риска]]</f>
         <v>0.63</v>
       </c>
-      <c r="I6" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Снижение. Старт с веб-аудита без установки и надстройки внутри Excel; собственный редактор — только после подтверждения спроса; бесплатный тизер находок. Ответственный: Владелец продукта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="78" customHeight="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I6" s="30" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="10">
         <v>4</v>
       </c>
@@ -2302,38 +2694,30 @@
         <f>"R "&amp;Таблица1[[#This Row],[Номер риска]]&amp;" "</f>
         <v xml:space="preserve">R 4 </v>
       </c>
-      <c r="C7" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Срыв сроков критического пути из-за недооценки трудоёмкости (ядро, надстройка)</t>
-        </is>
-      </c>
-      <c r="D7" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Высокое — сдвиг релиза, рост затрат на оплату труда</t>
-        </is>
-      </c>
-      <c r="E7" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Отставание &gt; 2 недель от базового плана на воротах</t>
-        </is>
-      </c>
-      <c r="F7" s="30">
+      <c r="C7" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="28">
         <v>0.8</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="28">
         <v>0.7</v>
       </c>
       <c r="H7" s="10">
         <f>Таблица1[[#This Row],[Оценка вероятности возникновения риска]]*Таблица1[[#This Row],[Оценка силы воздействия риска]]</f>
-        <v>0.56</v>
-      </c>
-      <c r="I7" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Снижение. Ворота фаз, еженедельный контроль по диаграмме Ганта; при отставании более 2 недель — второй бэкенд-разработчик и подрядчик на критические работы за счёт резерва; AI-агенты для типового кода; Should и Could в план не входят, объём Must не расширяется. Ответственный: Руководитель проекта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="78" customHeight="1" spans="1:9" x14ac:dyDescent="0.35">
+        <v>0.55999999999999994</v>
+      </c>
+      <c r="I7" s="30" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="10">
         <v>5</v>
       </c>
@@ -2341,38 +2725,30 @@
         <f>"R "&amp;Таблица1[[#This Row],[Номер риска]]&amp;" "</f>
         <v xml:space="preserve">R 5 </v>
       </c>
-      <c r="C8" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Пользователи не готовы загружать конфиденциальные финмодели в облако</t>
-        </is>
-      </c>
-      <c r="D8" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Высокое — низкая активация, мало данных для проверки ценности</t>
-        </is>
-      </c>
-      <c r="E8" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Отказы на шаге загрузки &gt; 70%</t>
-        </is>
-      </c>
-      <c r="F8" s="53">
+      <c r="C8" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="29">
         <v>0.5</v>
       </c>
-      <c r="G8" s="53">
+      <c r="G8" s="29">
         <v>0.8</v>
       </c>
       <c r="H8" s="10">
         <f>Таблица1[[#This Row],[Оценка вероятности возникновения риска]]*Таблица1[[#This Row],[Оценка силы воздействия риска]]</f>
         <v>0.4</v>
       </c>
-      <c r="I8" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Снижение. Блок доверия у загрузчика, хостинг в ЕС, удаление файлов по сроку, отказ от обучения на данных, демо-файл «проверить на примере». Ответственный: Руководитель проекта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="78" customHeight="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I8" s="30" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="10">
         <v>6</v>
       </c>
@@ -2380,20 +2756,14 @@
         <f>"R "&amp;Таблица1[[#This Row],[Номер риска]]&amp;" "</f>
         <v xml:space="preserve">R 6 </v>
       </c>
-      <c r="C9" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Сложные элементы xlsx (объединённые ячейки, массивы, локали, внешние ссылки) — расхождение пересчёта с Excel</t>
-        </is>
-      </c>
-      <c r="D9" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Среднее — ошибочные находки, сдвиг сроков разработки ядра</t>
-        </is>
-      </c>
-      <c r="E9" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Доля ошибок парсинга &gt; 5% на eval-наборе</t>
-        </is>
+      <c r="C9" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>57</v>
       </c>
       <c r="F9" s="10">
         <v>0.6</v>
@@ -2405,13 +2775,11 @@
         <f>Таблица1[[#This Row],[Оценка вероятности возникновения риска]]*Таблица1[[#This Row],[Оценка силы воздействия риска]]</f>
         <v>0.36</v>
       </c>
-      <c r="I9" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Снижение. Набор эталонных книг; сложные элементы только читаются с предупреждением и пометкой «проверено частично». Ответственный: Бэкенд-разработчик 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="78" customHeight="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I9" s="30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="10">
         <v>7</v>
       </c>
@@ -2419,20 +2787,14 @@
         <f>"R "&amp;Таблица1[[#This Row],[Номер риска]]&amp;" "</f>
         <v xml:space="preserve">R 7 </v>
       </c>
-      <c r="C10" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Уход или выгорание ключевого разработчика ядра верификации</t>
-        </is>
-      </c>
-      <c r="D10" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Высокое — потеря знаний, срыв сроков критического пути</t>
-        </is>
-      </c>
-      <c r="E10" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Снижение вовлечённости, переработки, внешнее предложение о работе</t>
-        </is>
+      <c r="C10" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>61</v>
       </c>
       <c r="F10" s="10">
         <v>0.4</v>
@@ -2442,15 +2804,13 @@
       </c>
       <c r="H10" s="10">
         <f>Таблица1[[#This Row],[Оценка вероятности возникновения риска]]*Таблица1[[#This Row],[Оценка силы воздействия риска]]</f>
-        <v>0.32</v>
-      </c>
-      <c r="I10" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Снижение. ADR и документация, обязательное код-ревью, совместное владение ядром двумя разработчиками, контроль нагрузки. Ответственный: Руководитель проекта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="78" customHeight="1" spans="1:9" x14ac:dyDescent="0.35">
+        <v>0.32000000000000006</v>
+      </c>
+      <c r="I10" s="30" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="10">
         <v>8</v>
       </c>
@@ -2458,20 +2818,14 @@
         <f>"R "&amp;Таблица1[[#This Row],[Номер риска]]&amp;" "</f>
         <v xml:space="preserve">R 8 </v>
       </c>
-      <c r="C11" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Рост цен или изменение условий LLM API</t>
-        </is>
-      </c>
-      <c r="D11" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Среднее — снижение валовой маржи ниже 65%</t>
-        </is>
-      </c>
-      <c r="E11" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Стоимость LLM &gt; 30% выручки на пользователя</t>
-        </is>
+      <c r="C11" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>65</v>
       </c>
       <c r="F11" s="10">
         <v>0.5</v>
@@ -2483,13 +2837,11 @@
         <f>Таблица1[[#This Row],[Оценка вероятности возникновения риска]]*Таблица1[[#This Row],[Оценка силы воздействия риска]]</f>
         <v>0.3</v>
       </c>
-      <c r="I11" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Снижение. LLM gateway с несколькими провайдерами, кэш промптов, эвристики до вызова LLM, лимиты тарифов. Ответственный: ML/LLM-инженер.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="78" customHeight="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I11" s="30" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="10">
         <v>9</v>
       </c>
@@ -2497,20 +2849,14 @@
         <f>"R "&amp;Таблица1[[#This Row],[Номер риска]]&amp;" "</f>
         <v xml:space="preserve">R 9 </v>
       </c>
-      <c r="C12" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Низкая конверсия Free → платный тариф (&lt; 2%)</t>
-        </is>
-      </c>
-      <c r="D12" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Высокое — цель «≥ 50 платящих пользователей» не достигнута</t>
-        </is>
-      </c>
-      <c r="E12" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Конверсия &lt; 2% через месяц после запуска оплаты</t>
-        </is>
+      <c r="C12" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>69</v>
       </c>
       <c r="F12" s="10">
         <v>0.5</v>
@@ -2522,13 +2868,11 @@
         <f>Таблица1[[#This Row],[Оценка вероятности возникновения риска]]*Таблица1[[#This Row],[Оценка силы воздействия риска]]</f>
         <v>0.35</v>
       </c>
-      <c r="I12" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Снижение. Оплата в точке максимальной ценности («исправить и скачать»), разовый аудит 9 €, пробный Pro 7 дней, A/B-тест цен. Ответственный: Владелец продукта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="78" customHeight="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I12" s="30" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="10">
         <v>10</v>
       </c>
@@ -2536,20 +2880,14 @@
         <f>"R "&amp;Таблица1[[#This Row],[Номер риска]]&amp;" "</f>
         <v xml:space="preserve">R 10 </v>
       </c>
-      <c r="C13" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Превышение бюджета проекта</t>
-        </is>
-      </c>
-      <c r="D13" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Среднее — нехватка средств на запуск и маркетинг</t>
-        </is>
-      </c>
-      <c r="E13" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Освоение бюджета опережает план более чем на 10%</t>
-        </is>
+      <c r="C13" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>73</v>
       </c>
       <c r="F13" s="10">
         <v>0.4</v>
@@ -2561,13 +2899,11 @@
         <f>Таблица1[[#This Row],[Оценка вероятности возникновения риска]]*Таблица1[[#This Row],[Оценка силы воздействия риска]]</f>
         <v>0.24</v>
       </c>
-      <c r="I13" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Принятие. Резерв 10% от базовой стоимости (47 000 BYN), ежемесячный контроль затрат, приоритизация Must have. Ответственный: Руководитель проекта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="78" customHeight="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I13" s="30" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="10">
         <v>11</v>
       </c>
@@ -2575,20 +2911,14 @@
         <f>"R "&amp;Таблица1[[#This Row],[Номер риска]]&amp;" "</f>
         <v xml:space="preserve">R 11 </v>
       </c>
-      <c r="C14" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лицензия движка пересчёта формул (например, GPLv3) несовместима с закрытым SaaS</t>
-        </is>
-      </c>
-      <c r="D14" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Высокое — замена библиотеки, +1–2 месяца на критическом пути</t>
-        </is>
-      </c>
-      <c r="E14" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Выбрана библиотека с copyleft-лицензией</t>
-        </is>
+      <c r="C14" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>77</v>
       </c>
       <c r="F14" s="10">
         <v>0.4</v>
@@ -2598,15 +2928,13 @@
       </c>
       <c r="H14" s="10">
         <f>Таблица1[[#This Row],[Оценка вероятности возникновения риска]]*Таблица1[[#This Row],[Оценка силы воздействия риска]]</f>
-        <v>0.28</v>
-      </c>
-      <c r="I14" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Уклонение. Проверка лицензий на этапе архитектуры, выбор permissive-библиотек или собственный пересчёт, проверка лицензий в CI. Ответственный: Бэкенд-разработчик 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="78" customHeight="1" spans="1:9" x14ac:dyDescent="0.35">
+        <v>0.27999999999999997</v>
+      </c>
+      <c r="I14" s="30" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="10">
         <v>12</v>
       </c>
@@ -2614,20 +2942,14 @@
         <f>"R "&amp;Таблица1[[#This Row],[Номер риска]]&amp;" "</f>
         <v xml:space="preserve">R 12 </v>
       </c>
-      <c r="C15" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Не удастся привлечь 10–20 пилотных пользователей с реальными финмоделями</t>
-        </is>
-      </c>
-      <c r="D15" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Высокое — нерепрезентативный eval-набор, правила настроены «вслепую»</t>
-        </is>
-      </c>
-      <c r="E15" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">К концу 2-го месяца &lt; 5 пилотных пользователей</t>
-        </is>
+      <c r="C15" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>81</v>
       </c>
       <c r="F15" s="10">
         <v>0.3</v>
@@ -2639,13 +2961,11 @@
         <f>Таблица1[[#This Row],[Оценка вероятности возникновения риска]]*Таблица1[[#This Row],[Оценка силы воздействия риска]]</f>
         <v>0.24</v>
       </c>
-      <c r="I15" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Снижение. Прямой выход на бухгалтерские и консалтинговые фирмы, бесплатный аудит шаблона, открытые финмодели как резерв. Ответственный: Руководитель проекта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="78" customHeight="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I15" s="30" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="10">
         <v>13</v>
       </c>
@@ -2653,20 +2973,14 @@
         <f>"R "&amp;Таблица1[[#This Row],[Номер риска]]&amp;" "</f>
         <v xml:space="preserve">R 13 </v>
       </c>
-      <c r="C16" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Нарушение GDPR / Закона РБ № 99-З «О защите персональных данных» при передаче данных LLM-провайдеру</t>
-        </is>
-      </c>
-      <c r="D16" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Критическое — штрафы, блокировка обработки, репутационный ущерб</t>
-        </is>
-      </c>
-      <c r="E16" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Нет DPA с провайдером; провайдер без обработки в ЕС</t>
-        </is>
+      <c r="C16" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>85</v>
       </c>
       <c r="F16" s="10">
         <v>0.3</v>
@@ -2678,13 +2992,11 @@
         <f>Таблица1[[#This Row],[Оценка вероятности возникновения риска]]*Таблица1[[#This Row],[Оценка силы воздействия риска]]</f>
         <v>0.27</v>
       </c>
-      <c r="I16" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Уклонение. Только провайдеры с zero data retention и регионом ЕС; DPA; реестр обработки; в LLM передаётся профиль таблицы, а не весь файл. Ответственный: Руководитель проекта (юрист).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="78" customHeight="1" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="I16" s="30" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="10">
         <v>14</v>
       </c>
@@ -2692,20 +3004,14 @@
         <f>"R "&amp;Таблица1[[#This Row],[Номер риска]]&amp;" "</f>
         <v xml:space="preserve">R 14 </v>
       </c>
-      <c r="C17" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Задержка или отказ в публикации надстройки в Microsoft AppSource</t>
-        </is>
-      </c>
-      <c r="D17" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Среднее — сдвиг публичного релиза основного продукта</t>
-        </is>
-      </c>
-      <c r="E17" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Замечания валидации AppSource; проверка дольше 4 недель</t>
-        </is>
+      <c r="C17" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="E17" s="30" t="s">
+        <v>89</v>
       </c>
       <c r="F17" s="10">
         <v>0.5</v>
@@ -2717,13 +3023,11 @@
         <f>Таблица1[[#This Row],[Оценка вероятности возникновения риска]]*Таблица1[[#This Row],[Оценка силы воздействия риска]]</f>
         <v>0.25</v>
       </c>
-      <c r="I17" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Снижение. Чек-лист валидации AppSource проходится на бете 13.0 и в тестировании 14.0; подача — в первый день работы 15.0 (01.09.2027), проверка до 4 недель укладывается в месяц работы; при задержке публичный запуск идёт через веб-аудит, надстройка публикуется позже. Ответственный: Фронтенд-разработчик.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="78" customHeight="1" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="I17" s="30" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="10">
         <v>15</v>
       </c>
@@ -2731,20 +3035,14 @@
         <f>"R "&amp;Таблица1[[#This Row],[Номер риска]]&amp;" "</f>
         <v xml:space="preserve">R 15 </v>
       </c>
-      <c r="C18" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Раздувание требований (собственный редактор, коннекторы, Google Sheets)</t>
-        </is>
-      </c>
-      <c r="D18" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Низкое — распыление ресурсов, задержка MVP до 2 недель</t>
-        </is>
-      </c>
-      <c r="E18" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Запросы вне списка Must/Should от заказчика и бета-пользователей</t>
-        </is>
+      <c r="C18" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>93</v>
       </c>
       <c r="F18" s="10">
         <v>0.6</v>
@@ -2756,13 +3054,11 @@
         <f>Таблица1[[#This Row],[Оценка вероятности возникновения риска]]*Таблица1[[#This Row],[Оценка силы воздействия риска]]</f>
         <v>0.24</v>
       </c>
-      <c r="I18" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Уклонение. Зафиксированный список Won’t have, процедура управления изменениями, бэклог v2. Ответственный: Владелец продукта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="78" customHeight="1" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="I18" s="30" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="10">
         <v>16</v>
       </c>
@@ -2770,38 +3066,30 @@
         <f>"R "&amp;Таблица1[[#This Row],[Номер риска]]&amp;" "</f>
         <v xml:space="preserve">R 16 </v>
       </c>
-      <c r="C19" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Утечка файлов клиентов (ошибка разграничения доступа, взлом)</t>
-        </is>
-      </c>
-      <c r="D19" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Критическое — штрафы, потеря доверия, закрытие B2B-продаж</t>
-        </is>
-      </c>
-      <c r="E19" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Аномальные запросы к хранилищу; критическая уязвимость в зависимостях</t>
-        </is>
+      <c r="C19" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>97</v>
       </c>
       <c r="F19" s="10">
         <v>0.2</v>
       </c>
       <c r="G19" s="10">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="10">
         <f>Таблица1[[#This Row],[Оценка вероятности возникновения риска]]*Таблица1[[#This Row],[Оценка силы воздействия риска]]</f>
         <v>0.2</v>
       </c>
-      <c r="I19" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Снижение + передача. RLS по воркспейсу, шифрование, песочница без сети, сканирование зависимостей, пентест; страхование киберрисков. Ответственный: Бэкенд-разработчик 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="78" customHeight="1" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="I19" s="30" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="10">
         <v>17</v>
       </c>
@@ -2809,20 +3097,14 @@
         <f>"R "&amp;Таблица1[[#This Row],[Номер риска]]&amp;" "</f>
         <v xml:space="preserve">R 17 </v>
       </c>
-      <c r="C20" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prompt injection через содержимое ячеек и текста документа</t>
-        </is>
-      </c>
-      <c r="D20" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Среднее — искажённые планы агента, утечка системного промпта</t>
-        </is>
-      </c>
-      <c r="E20" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Внедрённые инструкции из тестового набора проходят фильтр</t>
-        </is>
+      <c r="C20" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="30" t="s">
+        <v>101</v>
       </c>
       <c r="F20" s="10">
         <v>0.2</v>
@@ -2834,13 +3116,11 @@
         <f>Таблица1[[#This Row],[Оценка вероятности возникновения риска]]*Таблица1[[#This Row],[Оценка силы воздействия риска]]</f>
         <v>0.12</v>
       </c>
-      <c r="I20" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Снижение. Данные в помеченных блоках, у агента нет инструментов с внешними эффектами, верификация каждого плана. Ответственный: ML/LLM-инженер.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="78" customHeight="1" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="I20" s="30" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="10">
         <v>18</v>
       </c>
@@ -2848,20 +3128,14 @@
         <f>"R "&amp;Таблица1[[#This Row],[Номер риска]]&amp;" "</f>
         <v xml:space="preserve">R 18 </v>
       </c>
-      <c r="C21" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Искажение структуры, стилей или диаграмм xlsx при экспорте исправленного файла</t>
-        </is>
-      </c>
-      <c r="D21" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Среднее — пользователь получает повреждённую книгу, потеря доверия к исправлениям</t>
-        </is>
-      </c>
-      <c r="E21" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Регрессионный тест «до/после экспорта» показывает отличия вне исправленных ячеек</t>
-        </is>
+      <c r="C21" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>105</v>
       </c>
       <c r="F21" s="10">
         <v>0.4</v>
@@ -2873,13 +3147,11 @@
         <f>Таблица1[[#This Row],[Оценка вероятности возникновения риска]]*Таблица1[[#This Row],[Оценка силы воздействия риска]]</f>
         <v>0.2</v>
       </c>
-      <c r="I21" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Снижение. Точечная правка XML внутри исходного пакета xlsx вместо пересохранения; регрессионный тест экспорта; проверка открытия в Excel для Windows, Mac и веб. Ответственный: Бэкенд-разработчик 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="78" customHeight="1" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="I21" s="30" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="10">
         <v>19</v>
       </c>
@@ -2887,20 +3159,14 @@
         <f>"R "&amp;Таблица1[[#This Row],[Номер риска]]&amp;" "</f>
         <v xml:space="preserve">R 19 </v>
       </c>
-      <c r="C22" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Временная недоступность провайдера LLM</t>
-        </is>
-      </c>
-      <c r="D22" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Низкое — нет AI-объяснений и исправлений на время сбоя</t>
-        </is>
-      </c>
-      <c r="E22" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ошибки или таймауты API &gt; 5% за час</t>
-        </is>
+      <c r="C22" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>109</v>
       </c>
       <c r="F22" s="10">
         <v>0.4</v>
@@ -2912,25 +3178,23 @@
         <f>Таблица1[[#This Row],[Оценка вероятности возникновения риска]]*Таблица1[[#This Row],[Оценка силы воздействия риска]]</f>
         <v>0.12</v>
       </c>
-      <c r="I22" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Принятие. Проверки работают без LLM; шаблонные объяснения из каталога правил; переключение провайдера в gateway. Ответственный: ML/LLM-инженер.</t>
-        </is>
+      <c r="I22" s="30" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A19:I22 D4:E8 H4:I8 A4:B18 D9:I18">
-    <cfRule type="expression" dxfId="23" priority="6">
+    <cfRule type="expression" dxfId="14" priority="6">
       <formula>$H4&gt;0.505</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:I22 D4:E8 H4:I8 A4:B18 D9:I18">
-    <cfRule type="expression" dxfId="22" priority="5">
+    <cfRule type="expression" dxfId="13" priority="5">
       <formula>AND($H4&lt;0.14,$H4&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:I22 D4:E8 H4:I8 A4:B18 D9:I18">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>AND($H4&lt;=0.505,$H4&gt;=0.14)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2944,69 +3208,66 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Y60"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:P60"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="4.7265625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="6.81640625" style="6" customWidth="1"/>
-    <col min="3" max="12" width="9.7265625" style="6" customWidth="1"/>
-    <col min="13" max="13" width="5.7265625" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.7265625" style="6"/>
-    <col min="15" max="15" width="20.453125" style="6" customWidth="1"/>
+    <col min="1" max="1" width="4.73046875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="6.796875" style="6" customWidth="1"/>
+    <col min="3" max="12" width="9.73046875" style="6" customWidth="1"/>
+    <col min="13" max="13" width="5.73046875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.73046875" style="6"/>
+    <col min="15" max="15" width="20.46484375" style="6" customWidth="1"/>
     <col min="16" max="16" width="22" style="6" customWidth="1"/>
-    <col min="17" max="17" width="21.26953125" style="6" customWidth="1"/>
-    <col min="18" max="16384" width="8.7265625" style="6"/>
+    <col min="17" max="17" width="21.265625" style="6" customWidth="1"/>
+    <col min="18" max="16384" width="8.73046875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="12" t="str">
         <f>"Карта рисков для проекта "&amp;'Таблица с рисками'!C1</f>
-        <v xml:space="preserve">Карта рисков для проекта TableMind — AI-сервис проверки Excel-моделей (веб-аудит + надстройка Excel)</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+        <v>Карта рисков для проекта TableMind — AI-сервис проверки Excel-моделей (веб-аудит + надстройка Excel)</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A2" s="12"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K5" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K6" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K7" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K8" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K9" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="56" t="s">
+    <row r="27" spans="1:11" ht="47.55" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="33" t="s">
         <v>11</v>
       </c>
       <c r="B27" s="13" t="s">
@@ -3019,8 +3280,8 @@
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
     </row>
-    <row r="28" spans="1:24" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="56"/>
+    <row r="28" spans="1:11" ht="47.55" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="33"/>
       <c r="B28" s="13" t="s">
         <v>22</v>
       </c>
@@ -3035,8 +3296,8 @@
       <c r="J28" s="10"/>
       <c r="K28" s="10"/>
     </row>
-    <row r="29" spans="1:24" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="56"/>
+    <row r="29" spans="1:11" ht="47.55" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="33"/>
       <c r="B29" s="13" t="s">
         <v>24</v>
       </c>
@@ -3051,8 +3312,8 @@
       <c r="J29" s="10"/>
       <c r="K29" s="10"/>
     </row>
-    <row r="30" spans="1:24" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="56"/>
+    <row r="30" spans="1:11" ht="47.55" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="33"/>
       <c r="B30" s="13" t="s">
         <v>26</v>
       </c>
@@ -3067,8 +3328,8 @@
       <c r="J30" s="10"/>
       <c r="K30" s="10"/>
     </row>
-    <row r="31" spans="1:24" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="56"/>
+    <row r="31" spans="1:11" ht="47.55" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="33"/>
       <c r="B31" s="13">
         <v>0</v>
       </c>
@@ -3085,17 +3346,17 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="21"/>
-      <c r="B32" s="57" t="s">
+      <c r="B32" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="57"/>
-      <c r="D32" s="57"/>
-      <c r="E32" s="57"/>
-      <c r="F32" s="57"/>
-    </row>
-    <row r="33" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+    </row>
+    <row r="33" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B33" s="21"/>
       <c r="C33" s="22"/>
       <c r="D33" s="22"/>
@@ -3103,7 +3364,7 @@
       <c r="F33" s="22"/>
       <c r="G33" s="22"/>
     </row>
-    <row r="34" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B34" s="21"/>
       <c r="C34" s="22"/>
       <c r="D34" s="22"/>
@@ -3111,8 +3372,8 @@
       <c r="F34" s="22"/>
       <c r="G34" s="22"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A35" s="56" t="s">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A35" s="33" t="s">
         <v>11</v>
       </c>
       <c r="B35" s="6">
@@ -3129,8 +3390,8 @@
       <c r="K35" s="25"/>
       <c r="L35" s="25"/>
     </row>
-    <row r="36" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="56"/>
+    <row r="36" spans="1:16" ht="14.55" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="33"/>
       <c r="B36" s="6">
         <v>0.9</v>
       </c>
@@ -3148,8 +3409,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A37" s="56"/>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A37" s="33"/>
       <c r="B37" s="6">
         <v>0.8</v>
       </c>
@@ -3171,8 +3432,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="56"/>
+    <row r="38" spans="1:16" ht="14.55" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="33"/>
       <c r="B38" s="6">
         <v>0.7</v>
       </c>
@@ -3194,8 +3455,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A39" s="56"/>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A39" s="33"/>
       <c r="B39" s="6">
         <v>0.6</v>
       </c>
@@ -3217,8 +3478,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A40" s="56"/>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A40" s="33"/>
       <c r="B40" s="6">
         <v>0.5</v>
       </c>
@@ -3233,8 +3494,8 @@
       <c r="K40" s="26"/>
       <c r="L40" s="26"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A41" s="56"/>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A41" s="33"/>
       <c r="B41" s="6">
         <v>0.4</v>
       </c>
@@ -3249,8 +3510,8 @@
       <c r="K41" s="26"/>
       <c r="L41" s="26"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A42" s="56"/>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A42" s="33"/>
       <c r="B42" s="6">
         <v>0.3</v>
       </c>
@@ -3265,8 +3526,8 @@
       <c r="K42" s="26"/>
       <c r="L42" s="26"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A43" s="56"/>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A43" s="33"/>
       <c r="B43" s="6">
         <v>0.2</v>
       </c>
@@ -3281,8 +3542,8 @@
       <c r="K43" s="26"/>
       <c r="L43" s="26"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A44" s="56"/>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A44" s="33"/>
       <c r="B44" s="6">
         <v>0.1</v>
       </c>
@@ -3297,7 +3558,7 @@
       <c r="K44" s="18"/>
       <c r="L44" s="18"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.45">
       <c r="B45" s="6">
         <v>0</v>
       </c>
@@ -3332,23 +3593,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="E46" s="55" t="s">
+    <row r="46" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E46" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="F46" s="55"/>
-      <c r="G46" s="55"/>
-      <c r="H46" s="55"/>
-      <c r="I46" s="55"/>
-    </row>
-    <row r="47" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+    </row>
+    <row r="47" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="49" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="56" t="s">
+    <row r="48" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="49" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A49" s="33" t="s">
         <v>11</v>
       </c>
       <c r="B49" s="6">
@@ -3395,8 +3656,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="56"/>
+    <row r="50" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="33"/>
       <c r="B50" s="6">
         <v>0.9</v>
       </c>
@@ -3444,8 +3705,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="56"/>
+    <row r="51" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="33"/>
       <c r="B51" s="6">
         <v>0.8</v>
       </c>
@@ -3497,8 +3758,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="56"/>
+    <row r="52" spans="1:16" ht="24.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="33"/>
       <c r="B52" s="6">
         <v>0.7</v>
       </c>
@@ -3550,8 +3811,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A53" s="56"/>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A53" s="33"/>
       <c r="B53" s="6">
         <v>0.6</v>
       </c>
@@ -3603,8 +3864,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A54" s="56"/>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A54" s="33"/>
       <c r="B54" s="6">
         <v>0.5</v>
       </c>
@@ -3649,8 +3910,8 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A55" s="56"/>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A55" s="33"/>
       <c r="B55" s="6">
         <v>0.4</v>
       </c>
@@ -3695,8 +3956,8 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A56" s="56"/>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A56" s="33"/>
       <c r="B56" s="6">
         <v>0.3</v>
       </c>
@@ -3741,8 +4002,8 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A57" s="56"/>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A57" s="33"/>
       <c r="B57" s="6">
         <v>0.2</v>
       </c>
@@ -3787,8 +4048,8 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A58" s="56"/>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A58" s="33"/>
       <c r="B58" s="6">
         <v>0.1</v>
       </c>
@@ -3833,7 +4094,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.45">
       <c r="B59" s="6">
         <v>0</v>
       </c>
@@ -3868,14 +4129,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="E60" s="55" t="s">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="E60" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="F60" s="55"/>
-      <c r="G60" s="55"/>
-      <c r="H60" s="55"/>
-      <c r="I60" s="55"/>
+      <c r="F60" s="32"/>
+      <c r="G60" s="32"/>
+      <c r="H60" s="32"/>
+      <c r="I60" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="6">
